--- a/top_pairs_by_period_selected.xlsx
+++ b/top_pairs_by_period_selected.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +567,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>1.621499427487024</v>
+        <v>1.621499427487023</v>
       </c>
     </row>
     <row r="7">
@@ -843,7 +843,7 @@
         <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9966894377177214</v>
+        <v>0.9966894377177213</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9831824464379506</v>
+        <v>0.9831824464379505</v>
       </c>
     </row>
     <row r="20">
@@ -935,7 +935,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>0.930276975142076</v>
+        <v>0.9302769751420762</v>
       </c>
     </row>
     <row r="23">
@@ -981,7 +981,7 @@
         <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>0.918501782120034</v>
+        <v>0.9185017821200341</v>
       </c>
     </row>
     <row r="25">
@@ -1050,7 +1050,7 @@
         <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8257157883930872</v>
+        <v>0.8257157883930875</v>
       </c>
     </row>
     <row r="28">
@@ -1073,7 +1073,7 @@
         <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8169230855818908</v>
+        <v>0.816923085581891</v>
       </c>
     </row>
     <row r="29">
@@ -1119,7 +1119,7 @@
         <v>29</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8067784848543691</v>
+        <v>0.8067784848543693</v>
       </c>
     </row>
     <row r="31">
@@ -1165,7 +1165,7 @@
         <v>31</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7864076258905677</v>
+        <v>0.7864076258905679</v>
       </c>
     </row>
     <row r="33">
@@ -1234,7 +1234,7 @@
         <v>34</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7600278138057051</v>
+        <v>0.7600278138057053</v>
       </c>
     </row>
     <row r="36">
@@ -1280,7 +1280,7 @@
         <v>36</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7390681483837143</v>
+        <v>0.739068148383714</v>
       </c>
     </row>
     <row r="38">
@@ -1326,7 +1326,7 @@
         <v>38</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7065702017469366</v>
+        <v>0.7065702017469367</v>
       </c>
     </row>
     <row r="40">
@@ -1349,7 +1349,7 @@
         <v>39</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6948594512459543</v>
+        <v>0.6948594512459545</v>
       </c>
     </row>
     <row r="41">
@@ -1441,7 +1441,7 @@
         <v>43</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6410146527471672</v>
+        <v>0.6410146527471674</v>
       </c>
     </row>
     <row r="45">
@@ -1464,7 +1464,7 @@
         <v>44</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6351168250739545</v>
+        <v>0.6351168250739543</v>
       </c>
     </row>
     <row r="46">
@@ -1556,7 +1556,7 @@
         <v>48</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6152891032097177</v>
+        <v>0.615289103209718</v>
       </c>
     </row>
     <row r="50">
@@ -1579,7 +1579,7 @@
         <v>49</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6146047129473855</v>
+        <v>0.6146047129473857</v>
       </c>
     </row>
     <row r="51">
@@ -1694,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>1.986559406406737</v>
+        <v>1.986559406406736</v>
       </c>
     </row>
     <row r="56">
@@ -1947,7 +1947,7 @@
         <v>15</v>
       </c>
       <c r="E66" t="n">
-        <v>1.281333748875262</v>
+        <v>1.281333748875263</v>
       </c>
     </row>
     <row r="67">
@@ -2154,7 +2154,7 @@
         <v>24</v>
       </c>
       <c r="E75" t="n">
-        <v>1.023324420868839</v>
+        <v>1.023324420868838</v>
       </c>
     </row>
     <row r="76">
@@ -2177,7 +2177,7 @@
         <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>1.021630198133822</v>
+        <v>1.021630198133823</v>
       </c>
     </row>
     <row r="77">
@@ -2384,7 +2384,7 @@
         <v>34</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8490208624007085</v>
+        <v>0.8490208624007087</v>
       </c>
     </row>
     <row r="86">
@@ -2453,7 +2453,7 @@
         <v>37</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7875678795134726</v>
+        <v>0.787567879513473</v>
       </c>
     </row>
     <row r="89">
@@ -2476,7 +2476,7 @@
         <v>38</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7793236277460343</v>
+        <v>0.7793236277460345</v>
       </c>
     </row>
     <row r="90">
@@ -2522,7 +2522,7 @@
         <v>40</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7390643106013357</v>
+        <v>0.7390643106013359</v>
       </c>
     </row>
     <row r="92">
@@ -2545,7 +2545,7 @@
         <v>41</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7317469529218781</v>
+        <v>0.7317469529218783</v>
       </c>
     </row>
     <row r="93">
@@ -2568,7 +2568,7 @@
         <v>42</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7271895754552703</v>
+        <v>0.7271895754552705</v>
       </c>
     </row>
     <row r="94">
@@ -2591,7 +2591,7 @@
         <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7127864042183514</v>
+        <v>0.7127864042183516</v>
       </c>
     </row>
     <row r="95">
@@ -2637,7 +2637,7 @@
         <v>45</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7048277481926308</v>
+        <v>0.7048277481926306</v>
       </c>
     </row>
     <row r="97">
@@ -2683,7 +2683,7 @@
         <v>47</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6999011813240601</v>
+        <v>0.6999011813240603</v>
       </c>
     </row>
     <row r="99">
@@ -2706,7 +2706,7 @@
         <v>48</v>
       </c>
       <c r="E99" t="n">
-        <v>0.6992004493908606</v>
+        <v>0.6992004493908607</v>
       </c>
     </row>
     <row r="100">
@@ -2959,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="E110" t="n">
-        <v>1.610887905426787</v>
+        <v>1.610887905426788</v>
       </c>
     </row>
     <row r="111">
@@ -3005,7 +3005,7 @@
         <v>11</v>
       </c>
       <c r="E112" t="n">
-        <v>1.571289734225013</v>
+        <v>1.571289734225014</v>
       </c>
     </row>
     <row r="113">
@@ -3074,7 +3074,7 @@
         <v>14</v>
       </c>
       <c r="E115" t="n">
-        <v>1.497031035442067</v>
+        <v>1.497031035442066</v>
       </c>
     </row>
     <row r="116">
@@ -3304,7 +3304,7 @@
         <v>24</v>
       </c>
       <c r="E125" t="n">
-        <v>1.24271265505233</v>
+        <v>1.242712655052331</v>
       </c>
     </row>
     <row r="126">
@@ -3810,7 +3810,7 @@
         <v>46</v>
       </c>
       <c r="E147" t="n">
-        <v>0.9018846631115719</v>
+        <v>0.9018846631115721</v>
       </c>
     </row>
     <row r="148">
@@ -3879,7 +3879,7 @@
         <v>49</v>
       </c>
       <c r="E150" t="n">
-        <v>0.8671183044343949</v>
+        <v>0.8671183044343951</v>
       </c>
     </row>
     <row r="151">
@@ -4799,7 +4799,7 @@
         <v>39</v>
       </c>
       <c r="E190" t="n">
-        <v>0.9735463268907372</v>
+        <v>0.9735463268907374</v>
       </c>
     </row>
     <row r="191">
@@ -4845,7 +4845,7 @@
         <v>41</v>
       </c>
       <c r="E192" t="n">
-        <v>0.9690135793014809</v>
+        <v>0.969013579301481</v>
       </c>
     </row>
     <row r="193">
@@ -5098,7 +5098,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="n">
-        <v>2.96804951679828</v>
+        <v>2.968049516798281</v>
       </c>
     </row>
     <row r="204">
@@ -5788,7 +5788,7 @@
         <v>32</v>
       </c>
       <c r="E233" t="n">
-        <v>1.094419201126356</v>
+        <v>1.094419201126357</v>
       </c>
     </row>
     <row r="234">
@@ -5949,7 +5949,7 @@
         <v>39</v>
       </c>
       <c r="E240" t="n">
-        <v>1.061089999970324</v>
+        <v>1.061089999970325</v>
       </c>
     </row>
     <row r="241">
@@ -6156,7 +6156,7 @@
         <v>48</v>
       </c>
       <c r="E249" t="n">
-        <v>0.9842711964654813</v>
+        <v>0.9842711964654816</v>
       </c>
     </row>
     <row r="250">
@@ -7214,7 +7214,7 @@
         <v>44</v>
       </c>
       <c r="E295" t="n">
-        <v>1.355420717802028</v>
+        <v>1.355420717802029</v>
       </c>
     </row>
     <row r="296">
@@ -7421,7 +7421,7 @@
         <v>3</v>
       </c>
       <c r="E304" t="n">
-        <v>4.10661002534432</v>
+        <v>4.106610025344321</v>
       </c>
     </row>
     <row r="305">
@@ -9215,7 +9215,7 @@
         <v>31</v>
       </c>
       <c r="E382" t="n">
-        <v>2.271695331264747</v>
+        <v>2.271695331264746</v>
       </c>
     </row>
     <row r="383">
@@ -10020,7 +10020,7 @@
         <v>16</v>
       </c>
       <c r="E417" t="n">
-        <v>3.264279953480341</v>
+        <v>3.264279953480342</v>
       </c>
     </row>
     <row r="418">
@@ -10342,7 +10342,7 @@
         <v>30</v>
       </c>
       <c r="E431" t="n">
-        <v>2.620389913535989</v>
+        <v>2.620389913535988</v>
       </c>
     </row>
     <row r="432">
@@ -10779,7 +10779,7 @@
         <v>49</v>
       </c>
       <c r="E450" t="n">
-        <v>2.248563523044268</v>
+        <v>2.248563523044267</v>
       </c>
     </row>
     <row r="451">
@@ -10825,7 +10825,7 @@
         <v>1</v>
       </c>
       <c r="E452" t="n">
-        <v>5.011844182128315</v>
+        <v>5.011844182128316</v>
       </c>
     </row>
     <row r="453">
@@ -11262,7 +11262,7 @@
         <v>20</v>
       </c>
       <c r="E471" t="n">
-        <v>3.345926558933461</v>
+        <v>3.345926558933462</v>
       </c>
     </row>
     <row r="472">
